--- a/DUC_DCC_LogAPI/Files/reportDCC_Accept.xlsx
+++ b/DUC_DCC_LogAPI/Files/reportDCC_Accept.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\New_Project\DUC_DCC_LogAPI\DUC_DCC_LogAPI\Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\FBNWEB04\wwwroot\custappl\CRUDLogs\dccduc_Api_new\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B82532D0-0DD2-4954-BCFA-C932C62BD9E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC53836-7ED2-4FA1-ACCC-F789FE677025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{823880ED-C392-4FB6-8B13-B5946B380BBC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{823880ED-C392-4FB6-8B13-B5946B380BBC}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Report!$A$2:$Q$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Report!$A$2:$W$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>GROUP NAME</t>
   </si>
@@ -78,22 +78,46 @@
     <t>No.</t>
   </si>
   <si>
-    <t>Is not dcc</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> DCC Report Log Accept</t>
-  </si>
-  <si>
     <t>User Accept</t>
   </si>
   <si>
     <t>Date User Accept</t>
+  </si>
+  <si>
+    <t>Is  bu dcc</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DCC Audited Log Report</t>
+  </si>
+  <si>
+    <t>POSITION</t>
+  </si>
+  <si>
+    <t>Confirmed By</t>
+  </si>
+  <si>
+    <t>Confirmed Date</t>
+  </si>
+  <si>
+    <t>Edited By</t>
+  </si>
+  <si>
+    <t>Edited Date</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>Confirmed Event</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="d/m/yyyy\ h:mm"/>
+  </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -109,22 +133,23 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Cordia New"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Cordia New"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="20"/>
+      <b/>
+      <sz val="18"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Cordia New"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -184,27 +209,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -540,51 +574,63 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E32F00C-973C-4B55-B3A9-D24B59245FBF}">
-  <dimension ref="A1:Q2"/>
-  <sheetFormatPr defaultRowHeight="18.600000000000001" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:W2"/>
+  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="8.88671875" style="6"/>
-    <col min="2" max="2" width="23.6640625" style="5" customWidth="1"/>
-    <col min="3" max="3" width="22" style="5" customWidth="1"/>
-    <col min="4" max="4" width="18.21875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="26" style="5" customWidth="1"/>
-    <col min="6" max="6" width="89.21875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="17.21875" style="5" customWidth="1"/>
-    <col min="8" max="8" width="38.109375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="22.77734375" style="5" customWidth="1"/>
-    <col min="10" max="10" width="30.21875" style="5" customWidth="1"/>
-    <col min="11" max="11" width="17.88671875" style="5" customWidth="1"/>
+    <col min="1" max="1" width="8.88671875" style="5"/>
+    <col min="2" max="2" width="23.6640625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="22" style="6" customWidth="1"/>
+    <col min="4" max="4" width="18.21875" style="6" customWidth="1"/>
+    <col min="5" max="5" width="26" style="6" customWidth="1"/>
+    <col min="6" max="6" width="89.21875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="17.21875" style="6" customWidth="1"/>
+    <col min="8" max="8" width="38.109375" style="6" customWidth="1"/>
+    <col min="9" max="9" width="22.77734375" style="6" customWidth="1"/>
+    <col min="10" max="10" width="30.21875" style="6" customWidth="1"/>
+    <col min="11" max="11" width="17.88671875" style="6" customWidth="1"/>
     <col min="12" max="12" width="21.33203125" style="7" customWidth="1"/>
     <col min="13" max="13" width="40.6640625" style="7" customWidth="1"/>
     <col min="14" max="14" width="44.5546875" style="7" customWidth="1"/>
     <col min="15" max="15" width="15.5546875" style="7" customWidth="1"/>
-    <col min="16" max="16" width="30.21875" style="5" customWidth="1"/>
-    <col min="17" max="17" width="25.33203125" style="5" customWidth="1"/>
-    <col min="18" max="16384" width="8.88671875" style="2"/>
+    <col min="16" max="16" width="30.21875" style="6" customWidth="1"/>
+    <col min="17" max="17" width="25.33203125" style="6" customWidth="1"/>
+    <col min="18" max="18" width="30.21875" style="6" customWidth="1"/>
+    <col min="19" max="19" width="25.33203125" style="11" customWidth="1"/>
+    <col min="20" max="20" width="25.33203125" style="6" customWidth="1"/>
+    <col min="21" max="21" width="25.33203125" style="11" customWidth="1"/>
+    <col min="22" max="22" width="37.77734375" style="6" customWidth="1"/>
+    <col min="23" max="23" width="24.21875" style="8" customWidth="1"/>
+    <col min="24" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
-      <c r="M1" s="8"/>
-      <c r="N1" s="8"/>
-      <c r="O1" s="8"/>
-      <c r="P1" s="8"/>
-      <c r="Q1" s="8"/>
+    <row r="1" spans="1:23" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9"/>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:23" s="1" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -606,7 +652,9 @@
       <c r="G2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="3"/>
+      <c r="H2" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="I2" s="4" t="s">
         <v>6</v>
       </c>
@@ -626,19 +674,37 @@
         <v>11</v>
       </c>
       <c r="O2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="P2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="Q2" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
+      </c>
+      <c r="R2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="S2" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="T2" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="U2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="V2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:Q2" xr:uid="{8E32F00C-973C-4B55-B3A9-D24B59245FBF}"/>
+  <autoFilter ref="A2:W2" xr:uid="{8E32F00C-973C-4B55-B3A9-D24B59245FBF}"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A1:W1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/DUC_DCC_LogAPI/Files/reportDCC_Accept.xlsx
+++ b/DUC_DCC_LogAPI/Files/reportDCC_Accept.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\FBNWEB04\wwwroot\custappl\CRUDLogs\dccduc_Api_new\Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\New_Project\DUC_DCC_LogAPI\DUC_DCC_LogAPI\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAC53836-7ED2-4FA1-ACCC-F789FE677025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B411169E-B195-4BBD-A73B-2943BC9B75B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{823880ED-C392-4FB6-8B13-B5946B380BBC}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{823880ED-C392-4FB6-8B13-B5946B380BBC}"/>
   </bookViews>
   <sheets>
     <sheet name="Report" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Report!$A$2:$W$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Report!$A$2:$U$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>GROUP NAME</t>
   </si>
@@ -76,12 +76,6 @@
   </si>
   <si>
     <t>No.</t>
-  </si>
-  <si>
-    <t>User Accept</t>
-  </si>
-  <si>
-    <t>Date User Accept</t>
   </si>
   <si>
     <t>Is  bu dcc</t>
@@ -116,7 +110,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="d/m/yyyy\ h:mm"/>
+    <numFmt numFmtId="164" formatCode="d/m/yyyy\ h:mm"/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -231,14 +225,14 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -574,7 +568,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E32F00C-973C-4B55-B3A9-D24B59245FBF}">
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.6"/>
   <cols>
     <col min="1" max="1" width="8.88671875" style="5"/>
@@ -593,44 +587,40 @@
     <col min="14" max="14" width="44.5546875" style="7" customWidth="1"/>
     <col min="15" max="15" width="15.5546875" style="7" customWidth="1"/>
     <col min="16" max="16" width="30.21875" style="6" customWidth="1"/>
-    <col min="17" max="17" width="25.33203125" style="6" customWidth="1"/>
-    <col min="18" max="18" width="30.21875" style="6" customWidth="1"/>
-    <col min="19" max="19" width="25.33203125" style="11" customWidth="1"/>
-    <col min="20" max="20" width="25.33203125" style="6" customWidth="1"/>
-    <col min="21" max="21" width="25.33203125" style="11" customWidth="1"/>
-    <col min="22" max="22" width="37.77734375" style="6" customWidth="1"/>
-    <col min="23" max="23" width="24.21875" style="8" customWidth="1"/>
-    <col min="24" max="16384" width="8.88671875" style="2"/>
+    <col min="17" max="17" width="25.33203125" style="10" customWidth="1"/>
+    <col min="18" max="18" width="25.33203125" style="6" customWidth="1"/>
+    <col min="19" max="19" width="25.33203125" style="10" customWidth="1"/>
+    <col min="20" max="20" width="37.77734375" style="6" customWidth="1"/>
+    <col min="21" max="21" width="24.21875" style="8" customWidth="1"/>
+    <col min="22" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="9"/>
-      <c r="W1" s="9"/>
+    <row r="1" spans="1:21" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+      <c r="M1" s="11"/>
+      <c r="N1" s="11"/>
+      <c r="O1" s="11"/>
+      <c r="P1" s="11"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
     </row>
-    <row r="2" spans="1:23" s="1" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:21" s="1" customFormat="1" ht="20.399999999999999" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
         <v>12</v>
       </c>
@@ -653,7 +643,7 @@
         <v>5</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>6</v>
@@ -674,37 +664,31 @@
         <v>11</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q2" s="4" t="s">
-        <v>14</v>
+        <v>16</v>
+      </c>
+      <c r="Q2" s="9" t="s">
+        <v>17</v>
       </c>
       <c r="R2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="S2" s="10" t="s">
+      <c r="S2" s="9" t="s">
         <v>19</v>
       </c>
       <c r="T2" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="U2" s="10" t="s">
+      <c r="U2" s="4" t="s">
         <v>21</v>
-      </c>
-      <c r="V2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="W2" s="4" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:W2" xr:uid="{8E32F00C-973C-4B55-B3A9-D24B59245FBF}"/>
+  <autoFilter ref="A2:U2" xr:uid="{8E32F00C-973C-4B55-B3A9-D24B59245FBF}"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:W1"/>
+    <mergeCell ref="A1:U1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
